--- a/data/byouin_list/org/byouin_list.xlsx
+++ b/data/byouin_list/org/byouin_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\po3filesv07\政策局データ戦略課共用\2024年度\101_データ活用推進班★\202_オープンデータ\2024\★公開中データ（HP・BODIK共通）★\29_病院一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{739EBA6F-79EA-42AA-9EF7-7AF298E58683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C92B727-8E60-42DC-A356-0AB8FE6AF044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
@@ -991,7 +991,7 @@
     <t>木下　裕俊</t>
   </si>
   <si>
-    <t>桜十字熊本東病院</t>
+    <t>くまもと在宅支援病院</t>
   </si>
   <si>
     <t>862-0922</t>
@@ -1030,7 +1030,7 @@
     <t>防衛省</t>
   </si>
   <si>
-    <t>内藤　智子</t>
+    <t>中家　和宏</t>
   </si>
   <si>
     <t>昭和 32年08月01日</t>
@@ -2044,7 +2044,7 @@
     <t>伊東歯科口腔病院</t>
   </si>
   <si>
-    <t>861-0851</t>
+    <t>860-0851</t>
   </si>
   <si>
     <t xml:space="preserve">熊本市中央区子飼本町４番１４号 </t>
@@ -18265,7 +18265,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EA674AB-B398-4A1E-8989-7222AB7F3ECF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{949C706C-D88D-4E9C-87E7-8CC75E6A1A51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -18286,7 +18286,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F6050CD-9EDE-4974-9BB2-A8A03FDD9D64}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD28E777-D89C-43F5-8253-3064599C6401}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -18294,7 +18294,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35A85F85-E350-4528-A2D7-1C5DB622E87D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EA6F6E1-C231-4E28-AA87-D5433278B612}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/data/byouin_list/org/byouin_list.xlsx
+++ b/data/byouin_list/org/byouin_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\po3filesv07\政策局データ戦略課共用\2024年度\101_データ活用推進班★\202_オープンデータ\2024\★公開中データ（HP・BODIK共通）★\29_病院一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{739EBA6F-79EA-42AA-9EF7-7AF298E58683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1500E94-66D0-40C4-AE83-562B41E93211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
   </bookViews>
   <sheets>
     <sheet name="公開データ" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="756">
   <si>
     <t>施設区分</t>
   </si>
@@ -991,7 +991,7 @@
     <t>木下　裕俊</t>
   </si>
   <si>
-    <t>桜十字熊本東病院</t>
+    <t>くまもと在宅支援病院</t>
   </si>
   <si>
     <t>862-0922</t>
@@ -1030,7 +1030,7 @@
     <t>防衛省</t>
   </si>
   <si>
-    <t>内藤　智子</t>
+    <t>中家　和宏</t>
   </si>
   <si>
     <t>昭和 32年08月01日</t>
@@ -1510,7 +1510,7 @@
     <t>医療法人　尚和会</t>
   </si>
   <si>
-    <t>黒木　明彦</t>
+    <t>下村　康正</t>
   </si>
   <si>
     <t>昭和 27年08月08日</t>
@@ -1849,7 +1849,7 @@
     <t>社会医療法人　寿量会</t>
   </si>
   <si>
-    <t>中島　英親</t>
+    <t>寺本　憲市郎</t>
   </si>
   <si>
     <t>小児形成外科 血管外科 脳神経内科</t>
@@ -2044,7 +2044,7 @@
     <t>伊東歯科口腔病院</t>
   </si>
   <si>
-    <t>861-0851</t>
+    <t>860-0851</t>
   </si>
   <si>
     <t xml:space="preserve">熊本市中央区子飼本町４番１４号 </t>
@@ -2278,7 +2278,7 @@
     <t>医療法人　堀尾会</t>
   </si>
   <si>
-    <t>平田　好文</t>
+    <t>小原　健志</t>
   </si>
   <si>
     <t>小児リハビリテーション科 脳神経内科</t>
@@ -2347,7 +2347,7 @@
     <t>社会医療法人社団高野会</t>
   </si>
   <si>
-    <t>髙野　正太</t>
+    <t>辻　順行</t>
   </si>
   <si>
     <t>肛門内科 大腸・肛門リハビリテーション科 緩和ケア内科</t>
@@ -5540,9 +5540,7 @@
       <c r="X16" s="12"/>
       <c r="Y16" s="12"/>
       <c r="Z16" s="12"/>
-      <c r="AA16" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="AA16" s="12"/>
       <c r="AB16" s="12"/>
       <c r="AC16" s="12"/>
       <c r="AD16" s="12"/>
@@ -11429,9 +11427,7 @@
       <c r="AA52" s="12"/>
       <c r="AB52" s="12"/>
       <c r="AC52" s="12"/>
-      <c r="AD52" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="AD52" s="12"/>
       <c r="AE52" s="12"/>
       <c r="AF52" s="12"/>
       <c r="AG52" s="12"/>
@@ -13236,7 +13232,9 @@
       <c r="BT63" s="12"/>
       <c r="BU63" s="12"/>
       <c r="BV63" s="12"/>
-      <c r="BW63" s="12"/>
+      <c r="BW63" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="BX63" s="12"/>
       <c r="BY63" s="12"/>
       <c r="BZ63" s="12"/>
@@ -17953,8 +17951,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005D697BBB6C7C71438AA06DE92AE599CC" ma:contentTypeVersion="" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f36473a6175c50f896b3e1cbc3f13916">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31AAD03C-A983-4B16-863F-54F1EAB739D9" xmlns:ns3="77e41a71-2e1a-40e6-b4fe-2cfc7a738e36" xmlns:ns4="31aad03c-a983-4b16-863f-54f1eab739d9" xmlns:ns5="b1759036-c6d1-4f23-8159-9e5ddc0da7b4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f6313d8d0f967e45b58df0cfae536c6" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005D697BBB6C7C71438AA06DE92AE599CC" ma:contentTypeVersion="" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="a1eafba633277ec00883d4e10cd96e51">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31AAD03C-A983-4B16-863F-54F1EAB739D9" xmlns:ns3="77e41a71-2e1a-40e6-b4fe-2cfc7a738e36" xmlns:ns4="31aad03c-a983-4b16-863f-54f1eab739d9" xmlns:ns5="b1759036-c6d1-4f23-8159-9e5ddc0da7b4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="96273a645e27db515b242c1154665ce1" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="31AAD03C-A983-4B16-863F-54F1EAB739D9"/>
     <xsd:import namespace="77e41a71-2e1a-40e6-b4fe-2cfc7a738e36"/>
     <xsd:import namespace="31aad03c-a983-4b16-863f-54f1eab739d9"/>
@@ -18241,15 +18248,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -18265,7 +18263,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EA674AB-B398-4A1E-8989-7222AB7F3ECF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4561E363-8DC2-4498-9021-2BC05380028F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0CF70DC-688E-4770-BE0D-009205791C5D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -18285,16 +18291,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F6050CD-9EDE-4974-9BB2-A8A03FDD9D64}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35A85F85-E350-4528-A2D7-1C5DB622E87D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D68D3300-8546-4D5A-B2CF-C35276940E41}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/data/byouin_list/org/byouin_list.xlsx
+++ b/data/byouin_list/org/byouin_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\po3filesv07\政策局データ戦略課共用\2024年度\101_データ活用推進班★\202_オープンデータ\2024\★公開中データ（HP・BODIK共通）★\29_病院一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{739EBA6F-79EA-42AA-9EF7-7AF298E58683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1F350A1-9389-49AE-A96F-0B348B920720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="754">
   <si>
     <t>施設区分</t>
   </si>
@@ -703,7 +703,7 @@
     <t>鶴崎　成幸</t>
   </si>
   <si>
-    <t>脳神経内科 糖尿病・代謝内科</t>
+    <t>糖尿病・代謝内科</t>
   </si>
   <si>
     <t>昭和 48年07月16日</t>
@@ -991,7 +991,7 @@
     <t>木下　裕俊</t>
   </si>
   <si>
-    <t>桜十字熊本東病院</t>
+    <t>くまもと在宅支援病院</t>
   </si>
   <si>
     <t>862-0922</t>
@@ -1030,7 +1030,7 @@
     <t>防衛省</t>
   </si>
   <si>
-    <t>内藤　智子</t>
+    <t>中家　和宏</t>
   </si>
   <si>
     <t>昭和 32年08月01日</t>
@@ -1315,7 +1315,7 @@
     <t>医療法人社団　ピネル会</t>
   </si>
   <si>
-    <t>竹内　良輔</t>
+    <t>竹内　有輔</t>
   </si>
   <si>
     <t>昭和 46年11月30日</t>
@@ -1468,9 +1468,6 @@
     <t>吉田　俊彰</t>
   </si>
   <si>
-    <t>糖尿病・代謝内科</t>
-  </si>
-  <si>
     <t>昭和 26年08月01日</t>
   </si>
   <si>
@@ -1510,7 +1507,7 @@
     <t>医療法人　尚和会</t>
   </si>
   <si>
-    <t>黒木　明彦</t>
+    <t>下村　康正</t>
   </si>
   <si>
     <t>昭和 27年08月08日</t>
@@ -1849,7 +1846,7 @@
     <t>社会医療法人　寿量会</t>
   </si>
   <si>
-    <t>中島　英親</t>
+    <t>寺本　憲市郎</t>
   </si>
   <si>
     <t>小児形成外科 血管外科 脳神経内科</t>
@@ -1942,7 +1939,7 @@
     <t>昭和 60年01月31日</t>
   </si>
   <si>
-    <t>くまもと乳腺・胃腸外科病院</t>
+    <t>くまもと乳腺外科病院</t>
   </si>
   <si>
     <t xml:space="preserve">熊本市中央区南熊本4丁目3-5 </t>
@@ -1954,7 +1951,7 @@
     <t>医療法人社団　世安会</t>
   </si>
   <si>
-    <t>澤田　俊彦</t>
+    <t>村本　一浩</t>
   </si>
   <si>
     <t>乳腺内科 がん化学療法内科</t>
@@ -2044,7 +2041,7 @@
     <t>伊東歯科口腔病院</t>
   </si>
   <si>
-    <t>861-0851</t>
+    <t>860-0851</t>
   </si>
   <si>
     <t xml:space="preserve">熊本市中央区子飼本町４番１４号 </t>
@@ -2077,7 +2074,7 @@
     <t>熊本市</t>
   </si>
   <si>
-    <t>掃本　誠治</t>
+    <t>三角　郁夫</t>
   </si>
   <si>
     <t>平成 22年03月23日</t>
@@ -2161,7 +2158,7 @@
     <t>社会医療法人令和会</t>
   </si>
   <si>
-    <t>平川　敬</t>
+    <t>生田　拓也</t>
   </si>
   <si>
     <t>血管外科</t>
@@ -2260,9 +2257,6 @@
     <t>坂本　憲史</t>
   </si>
   <si>
-    <t>内視鏡内科</t>
-  </si>
-  <si>
     <t>平成 24年08月01日</t>
   </si>
   <si>
@@ -2278,7 +2272,7 @@
     <t>医療法人　堀尾会</t>
   </si>
   <si>
-    <t>平田　好文</t>
+    <t>小原　健志</t>
   </si>
   <si>
     <t>小児リハビリテーション科 脳神経内科</t>
@@ -2347,7 +2341,7 @@
     <t>社会医療法人社団高野会</t>
   </si>
   <si>
-    <t>髙野　正太</t>
+    <t>辻　順行</t>
   </si>
   <si>
     <t>肛門内科 大腸・肛門リハビリテーション科 緩和ケア内科</t>
@@ -2413,7 +2407,7 @@
     <t>医療法人社団　井上会</t>
   </si>
   <si>
-    <t>木村　竜也</t>
+    <t>井上　佳子</t>
   </si>
   <si>
     <t>昭和 56年01月01日</t>
@@ -2804,19 +2798,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:DN91"/>
-  <sheetFormatPr defaultRowHeight="24.95" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="2" customWidth="1"/>
-    <col min="8" max="12" width="4.28515625" style="2" customWidth="1"/>
-    <col min="13" max="116" width="3.7109375" style="5" customWidth="1"/>
-    <col min="117" max="118" width="18.42578125" style="4" customWidth="1"/>
-    <col min="119" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="6.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="2" customWidth="1"/>
+    <col min="8" max="12" width="4.33203125" style="2" customWidth="1"/>
+    <col min="13" max="116" width="3.6640625" style="5" customWidth="1"/>
+    <col min="117" max="118" width="18.44140625" style="4" customWidth="1"/>
+    <col min="119" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:118" s="1" customFormat="1" ht="142.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -3175,27 +3169,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:118" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:118" s="3" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>665</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>666</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>667</v>
       </c>
       <c r="H2" s="9">
         <v>0</v>
@@ -3335,33 +3329,33 @@
         <v>125</v>
       </c>
       <c r="DM2" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="DN2" s="11" t="s">
         <v>668</v>
       </c>
-      <c r="DN2" s="11" t="s">
-        <v>669</v>
-      </c>
     </row>
-    <row r="3" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>677</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>680</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>681</v>
       </c>
       <c r="H3" s="9">
         <v>0</v>
@@ -3535,33 +3529,33 @@
         <v>125</v>
       </c>
       <c r="DM3" s="11" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="DN3" s="11" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
-    <row r="4" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>520</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>521</v>
       </c>
       <c r="H4" s="9">
         <v>0</v>
@@ -3699,33 +3693,33 @@
       <c r="DK4" s="12"/>
       <c r="DL4" s="12"/>
       <c r="DM4" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="DN4" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="DN4" s="11" t="s">
-        <v>523</v>
-      </c>
     </row>
-    <row r="5" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>727</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>729</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -3865,33 +3859,33 @@
         <v>125</v>
       </c>
       <c r="DM5" s="11" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="DN5" s="11" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
-    <row r="6" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>199</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>734</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>736</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -4051,33 +4045,33 @@
         <v>125</v>
       </c>
       <c r="DM6" s="11" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="DN6" s="11" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="7" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>711</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>712</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>714</v>
       </c>
       <c r="H7" s="9">
         <v>193</v>
@@ -4202,30 +4196,30 @@
       <c r="DL7" s="12"/>
       <c r="DM7" s="11"/>
       <c r="DN7" s="11" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
-    <row r="8" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>716</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>719</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>721</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -4323,7 +4317,9 @@
       <c r="BY8" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="BZ8" s="12"/>
+      <c r="BZ8" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="CA8" s="12"/>
       <c r="CB8" s="12"/>
       <c r="CC8" s="12"/>
@@ -4367,33 +4363,33 @@
         <v>125</v>
       </c>
       <c r="DM8" s="11" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="DN8" s="11" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
-    <row r="9" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>207</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>704</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>706</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -4529,33 +4525,33 @@
       <c r="DK9" s="12"/>
       <c r="DL9" s="12"/>
       <c r="DM9" s="11" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="DN9" s="11" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
-    <row r="10" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>696</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>698</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>699</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -4577,9 +4573,7 @@
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
-      <c r="P10" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
@@ -4608,9 +4602,7 @@
       <c r="AP10" s="12"/>
       <c r="AQ10" s="12"/>
       <c r="AR10" s="12"/>
-      <c r="AS10" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="AS10" s="12"/>
       <c r="AT10" s="12"/>
       <c r="AU10" s="12"/>
       <c r="AV10" s="12"/>
@@ -4619,7 +4611,9 @@
       <c r="AY10" s="12"/>
       <c r="AZ10" s="12"/>
       <c r="BA10" s="12"/>
-      <c r="BB10" s="12"/>
+      <c r="BB10" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="BC10" s="12"/>
       <c r="BD10" s="12"/>
       <c r="BE10" s="12"/>
@@ -4640,7 +4634,9 @@
       <c r="BT10" s="12"/>
       <c r="BU10" s="12"/>
       <c r="BV10" s="12"/>
-      <c r="BW10" s="12"/>
+      <c r="BW10" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="BX10" s="12"/>
       <c r="BY10" s="12"/>
       <c r="BZ10" s="12"/>
@@ -4683,35 +4679,35 @@
       <c r="DI10" s="12"/>
       <c r="DJ10" s="12"/>
       <c r="DK10" s="12"/>
-      <c r="DL10" s="12"/>
-      <c r="DM10" s="11" t="s">
-        <v>700</v>
-      </c>
+      <c r="DL10" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="DM10" s="11"/>
       <c r="DN10" s="11" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
-    <row r="11" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>319</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>690</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>691</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>370</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -4846,30 +4842,30 @@
         <v>196</v>
       </c>
       <c r="DN11" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
-    <row r="12" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>144</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>595</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>597</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>598</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -4942,17 +4938,11 @@
       <c r="BJ12" s="12"/>
       <c r="BK12" s="12"/>
       <c r="BL12" s="12"/>
-      <c r="BM12" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BM12" s="12"/>
       <c r="BN12" s="12"/>
-      <c r="BO12" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BO12" s="12"/>
       <c r="BP12" s="12"/>
-      <c r="BQ12" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BQ12" s="12"/>
       <c r="BR12" s="12"/>
       <c r="BS12" s="12"/>
       <c r="BT12" s="12"/>
@@ -5005,33 +4995,33 @@
         <v>125</v>
       </c>
       <c r="DM12" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="DN12" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="DN12" s="11" t="s">
-        <v>600</v>
-      </c>
     </row>
-    <row r="13" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>265</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>686</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>687</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -5160,30 +5150,30 @@
       <c r="DL13" s="12"/>
       <c r="DM13" s="11"/>
       <c r="DN13" s="11" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
-    <row r="14" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>634</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>637</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>638</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>639</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -5320,30 +5310,30 @@
       <c r="DL14" s="12"/>
       <c r="DM14" s="11"/>
       <c r="DN14" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
-    <row r="15" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>630</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>631</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>632</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -5476,31 +5466,31 @@
       </c>
       <c r="DM15" s="11"/>
       <c r="DN15" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
-    <row r="16" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>144</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>622</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="F16" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>624</v>
-      </c>
       <c r="H16" s="9">
         <v>0</v>
       </c>
@@ -5511,10 +5501,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="9">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="L16" s="9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M16" s="12" t="s">
         <v>125</v>
@@ -5540,9 +5530,7 @@
       <c r="X16" s="12"/>
       <c r="Y16" s="12"/>
       <c r="Z16" s="12"/>
-      <c r="AA16" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="AA16" s="12"/>
       <c r="AB16" s="12"/>
       <c r="AC16" s="12"/>
       <c r="AD16" s="12"/>
@@ -5645,33 +5633,33 @@
       <c r="DK16" s="12"/>
       <c r="DL16" s="12"/>
       <c r="DM16" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="DN16" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="DN16" s="11" t="s">
-        <v>626</v>
-      </c>
     </row>
-    <row r="17" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>609</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>610</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>611</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>612</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -5808,10 +5796,10 @@
       </c>
       <c r="DM17" s="11"/>
       <c r="DN17" s="11" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
-    <row r="18" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9" t="s">
         <v>118</v>
       </c>
@@ -5963,7 +5951,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="19" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="9" t="s">
         <v>118</v>
       </c>
@@ -6121,27 +6109,27 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>251</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="F20" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>604</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>605</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -6280,30 +6268,30 @@
       </c>
       <c r="DM20" s="11"/>
       <c r="DN20" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
-    <row r="21" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>505</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>506</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -6433,13 +6421,13 @@
       <c r="DK21" s="12"/>
       <c r="DL21" s="12"/>
       <c r="DM21" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="DN21" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="DN21" s="11" t="s">
-        <v>508</v>
-      </c>
     </row>
-    <row r="22" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="9" t="s">
         <v>118</v>
       </c>
@@ -6595,7 +6583,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="23" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="9" t="s">
         <v>118</v>
       </c>
@@ -6755,7 +6743,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="24" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="9" t="s">
         <v>118</v>
       </c>
@@ -6925,7 +6913,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="25" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="9" t="s">
         <v>118</v>
       </c>
@@ -7097,7 +7085,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="26" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="9" t="s">
         <v>118</v>
       </c>
@@ -7245,7 +7233,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="27" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="9" t="s">
         <v>118</v>
       </c>
@@ -7403,7 +7391,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>118</v>
       </c>
@@ -7591,7 +7579,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="9" t="s">
         <v>118</v>
       </c>
@@ -7749,7 +7737,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="30" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="9" t="s">
         <v>118</v>
       </c>
@@ -7913,7 +7901,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="31" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="9" t="s">
         <v>118</v>
       </c>
@@ -8103,7 +8091,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="32" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="9" t="s">
         <v>118</v>
       </c>
@@ -8261,7 +8249,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="9" t="s">
         <v>118</v>
       </c>
@@ -8411,7 +8399,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="9" t="s">
         <v>118</v>
       </c>
@@ -8559,27 +8547,27 @@
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B35" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="D35" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="E35" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="F35" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="G35" s="9" t="s">
         <v>513</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>514</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -8723,13 +8711,13 @@
         <v>125</v>
       </c>
       <c r="DM35" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="DN35" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="DN35" s="11" t="s">
-        <v>516</v>
-      </c>
     </row>
-    <row r="36" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="9" t="s">
         <v>118</v>
       </c>
@@ -8907,27 +8895,27 @@
         <v>422</v>
       </c>
     </row>
-    <row r="37" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B37" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="D37" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="E37" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="F37" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="G37" s="9" t="s">
         <v>549</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>550</v>
       </c>
       <c r="H37" s="9">
         <v>135</v>
@@ -9054,10 +9042,10 @@
       <c r="DL37" s="12"/>
       <c r="DM37" s="11"/>
       <c r="DN37" s="11" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="9" t="s">
         <v>118</v>
       </c>
@@ -9207,27 +9195,27 @@
         <v>205</v>
       </c>
     </row>
-    <row r="39" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B39" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="D39" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="E39" s="9" t="s">
         <v>643</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="F39" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="G39" s="9" t="s">
         <v>645</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>646</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -9366,10 +9354,10 @@
       </c>
       <c r="DM39" s="11"/>
       <c r="DN39" s="11" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
-    <row r="40" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="9" t="s">
         <v>118</v>
       </c>
@@ -9526,10 +9514,10 @@
       <c r="DL40" s="12"/>
       <c r="DM40" s="11"/>
       <c r="DN40" s="11" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
-    <row r="41" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="9" t="s">
         <v>118</v>
       </c>
@@ -9708,10 +9696,10 @@
       </c>
       <c r="DM41" s="11"/>
       <c r="DN41" s="11" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
-    <row r="42" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="9" t="s">
         <v>118</v>
       </c>
@@ -9877,7 +9865,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="43" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="9" t="s">
         <v>118</v>
       </c>
@@ -10027,7 +10015,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="44" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="9" t="s">
         <v>118</v>
       </c>
@@ -10181,27 +10169,27 @@
         <v>168</v>
       </c>
     </row>
-    <row r="45" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>251</v>
       </c>
       <c r="D45" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="F45" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="G45" s="9" t="s">
         <v>591</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>592</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -10340,30 +10328,30 @@
       </c>
       <c r="DM45" s="11"/>
       <c r="DN45" s="11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
-    <row r="46" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B46" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="D46" s="9" t="s">
+      <c r="E46" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="F46" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="G46" s="9" t="s">
         <v>541</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>542</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -10478,7 +10466,9 @@
       <c r="BR46" s="12"/>
       <c r="BS46" s="12"/>
       <c r="BT46" s="12"/>
-      <c r="BU46" s="12"/>
+      <c r="BU46" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="BV46" s="12"/>
       <c r="BW46" s="12" t="s">
         <v>125</v>
@@ -10549,13 +10539,13 @@
         <v>125</v>
       </c>
       <c r="DM46" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="DN46" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="DN46" s="11" t="s">
-        <v>544</v>
-      </c>
     </row>
-    <row r="47" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="9" t="s">
         <v>118</v>
       </c>
@@ -10717,27 +10707,27 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B48" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="D48" s="9" t="s">
+      <c r="E48" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="F48" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="G48" s="9" t="s">
         <v>555</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>556</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -10866,30 +10856,30 @@
       <c r="DL48" s="12"/>
       <c r="DM48" s="11"/>
       <c r="DN48" s="11" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
-    <row r="49" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B49" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="D49" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="E49" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="F49" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="G49" s="9" t="s">
         <v>562</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>563</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -10985,9 +10975,7 @@
       <c r="BW49" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="BX49" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BX49" s="12"/>
       <c r="BY49" s="12" t="s">
         <v>125</v>
       </c>
@@ -11041,13 +11029,13 @@
         <v>125</v>
       </c>
       <c r="DM49" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="DN49" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="DN49" s="11" t="s">
-        <v>565</v>
-      </c>
     </row>
-    <row r="50" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="9" t="s">
         <v>118</v>
       </c>
@@ -11223,27 +11211,27 @@
         <v>352</v>
       </c>
     </row>
-    <row r="51" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B51" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="E51" s="9" t="s">
         <v>747</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="F51" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="G51" s="9" t="s">
         <v>749</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>751</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -11370,10 +11358,10 @@
       <c r="DL51" s="12"/>
       <c r="DM51" s="11"/>
       <c r="DN51" s="11" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
-    <row r="52" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="9" t="s">
         <v>118</v>
       </c>
@@ -11429,9 +11417,7 @@
       <c r="AA52" s="12"/>
       <c r="AB52" s="12"/>
       <c r="AC52" s="12"/>
-      <c r="AD52" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="AD52" s="12"/>
       <c r="AE52" s="12"/>
       <c r="AF52" s="12"/>
       <c r="AG52" s="12"/>
@@ -11446,7 +11432,9 @@
       <c r="AP52" s="12"/>
       <c r="AQ52" s="12"/>
       <c r="AR52" s="12"/>
-      <c r="AS52" s="12"/>
+      <c r="AS52" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="AT52" s="12"/>
       <c r="AU52" s="12"/>
       <c r="AV52" s="12"/>
@@ -11531,27 +11519,27 @@
         <v>414</v>
       </c>
     </row>
-    <row r="53" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B53" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="C53" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="D53" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="E53" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="F53" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="G53" s="9" t="s">
         <v>570</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>571</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
@@ -11678,10 +11666,10 @@
       </c>
       <c r="DM53" s="11"/>
       <c r="DN53" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
-    <row r="54" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="9" t="s">
         <v>118</v>
       </c>
@@ -11833,27 +11821,27 @@
         <v>365</v>
       </c>
     </row>
-    <row r="55" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B55" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="C55" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="D55" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="E55" s="9" t="s">
         <v>532</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="F55" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="G55" s="9" t="s">
         <v>534</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>535</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
@@ -11981,33 +11969,33 @@
         <v>125</v>
       </c>
       <c r="DM55" s="11" t="s">
+        <v>535</v>
+      </c>
+      <c r="DN55" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="DN55" s="11" t="s">
-        <v>537</v>
-      </c>
     </row>
-    <row r="56" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B56" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="C56" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="D56" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="E56" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="F56" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="G56" s="9" t="s">
         <v>527</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>528</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -12148,30 +12136,30 @@
       <c r="DL56" s="12"/>
       <c r="DM56" s="11"/>
       <c r="DN56" s="11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
-    <row r="57" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B57" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C57" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="D57" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="E57" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="F57" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="G57" s="9" t="s">
         <v>442</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>443</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -12318,10 +12306,10 @@
       <c r="DL57" s="12"/>
       <c r="DM57" s="11"/>
       <c r="DN57" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="58" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="9" t="s">
         <v>118</v>
       </c>
@@ -12475,7 +12463,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="59" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="9" t="s">
         <v>118</v>
       </c>
@@ -12633,27 +12621,27 @@
         <v>372</v>
       </c>
     </row>
-    <row r="60" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B60" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="C60" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="D60" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="E60" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="F60" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="G60" s="9" t="s">
         <v>618</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>619</v>
       </c>
       <c r="H60" s="9">
         <v>190</v>
@@ -12784,10 +12772,10 @@
       <c r="DL60" s="12"/>
       <c r="DM60" s="11"/>
       <c r="DN60" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
-    <row r="61" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="9" t="s">
         <v>118</v>
       </c>
@@ -12878,9 +12866,7 @@
       <c r="BB61" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="BC61" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BC61" s="12"/>
       <c r="BD61" s="12"/>
       <c r="BE61" s="12"/>
       <c r="BF61" s="12"/>
@@ -12955,7 +12941,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="9" t="s">
         <v>118</v>
       </c>
@@ -13125,27 +13111,27 @@
         <v>325</v>
       </c>
     </row>
-    <row r="63" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B63" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="C63" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="D63" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="E63" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="F63" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="F63" s="9" t="s">
+      <c r="G63" s="9" t="s">
         <v>584</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>585</v>
       </c>
       <c r="H63" s="9">
         <v>0</v>
@@ -13236,7 +13222,9 @@
       <c r="BT63" s="12"/>
       <c r="BU63" s="12"/>
       <c r="BV63" s="12"/>
-      <c r="BW63" s="12"/>
+      <c r="BW63" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="BX63" s="12"/>
       <c r="BY63" s="12"/>
       <c r="BZ63" s="12"/>
@@ -13283,13 +13271,13 @@
       <c r="DK63" s="12"/>
       <c r="DL63" s="12"/>
       <c r="DM63" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="DN63" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="DN63" s="11" t="s">
-        <v>587</v>
-      </c>
     </row>
-    <row r="64" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="9" t="s">
         <v>118</v>
       </c>
@@ -13473,7 +13461,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="65" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="9" t="s">
         <v>118</v>
       </c>
@@ -13623,27 +13611,27 @@
         <v>386</v>
       </c>
     </row>
-    <row r="66" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B66" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="D66" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="E66" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="E66" s="9" t="s">
+      <c r="F66" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="G66" s="9" t="s">
         <v>485</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>486</v>
       </c>
       <c r="H66" s="9">
         <v>234</v>
@@ -13770,30 +13758,30 @@
       <c r="DL66" s="12"/>
       <c r="DM66" s="11"/>
       <c r="DN66" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
-    <row r="67" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B67" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="C67" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="D67" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="E67" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="F67" s="9" t="s">
         <v>673</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="G67" s="9" t="s">
         <v>674</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>675</v>
       </c>
       <c r="H67" s="9">
         <v>78</v>
@@ -13944,10 +13932,10 @@
         <v>196</v>
       </c>
       <c r="DN67" s="11" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
-    <row r="68" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="9" t="s">
         <v>118</v>
       </c>
@@ -14103,27 +14091,27 @@
         <v>345</v>
       </c>
     </row>
-    <row r="69" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B69" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="C69" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="D69" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="D69" s="9" t="s">
+      <c r="E69" s="9" t="s">
         <v>657</v>
       </c>
-      <c r="E69" s="9" t="s">
+      <c r="F69" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="F69" s="9" t="s">
+      <c r="G69" s="9" t="s">
         <v>659</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>660</v>
       </c>
       <c r="H69" s="9">
         <v>0</v>
@@ -14258,30 +14246,30 @@
       <c r="DL69" s="12"/>
       <c r="DM69" s="11"/>
       <c r="DN69" s="11" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
-    <row r="70" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B70" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="C70" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="D70" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="D70" s="9" t="s">
+      <c r="E70" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="E70" s="9" t="s">
+      <c r="F70" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="F70" s="9" t="s">
+      <c r="G70" s="9" t="s">
         <v>577</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>578</v>
       </c>
       <c r="H70" s="9">
         <v>0</v>
@@ -14426,30 +14414,30 @@
       <c r="DL70" s="12"/>
       <c r="DM70" s="11"/>
       <c r="DN70" s="11" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
-    <row r="71" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B71" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="C71" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="D71" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="E71" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="E71" s="9" t="s">
+      <c r="F71" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="G71" s="9" t="s">
         <v>456</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>457</v>
       </c>
       <c r="H71" s="9">
         <v>160</v>
@@ -14574,30 +14562,30 @@
       <c r="DL71" s="12"/>
       <c r="DM71" s="11"/>
       <c r="DN71" s="11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
-    <row r="72" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B72" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="C72" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="D72" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="D72" s="9" t="s">
+      <c r="E72" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="E72" s="9" t="s">
+      <c r="F72" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="G72" s="9" t="s">
         <v>652</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>653</v>
       </c>
       <c r="H72" s="9">
         <v>198</v>
@@ -14726,10 +14714,10 @@
       <c r="DL72" s="12"/>
       <c r="DM72" s="11"/>
       <c r="DN72" s="11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
-    <row r="73" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="9" t="s">
         <v>118</v>
       </c>
@@ -14877,7 +14865,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="74" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="9" t="s">
         <v>118</v>
       </c>
@@ -15053,27 +15041,27 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B75" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C75" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="D75" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="D75" s="9" t="s">
+      <c r="E75" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="E75" s="9" t="s">
+      <c r="F75" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="F75" s="9" t="s">
+      <c r="G75" s="9" t="s">
         <v>463</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>464</v>
       </c>
       <c r="H75" s="9">
         <v>199</v>
@@ -15200,30 +15188,30 @@
       <c r="DL75" s="12"/>
       <c r="DM75" s="11"/>
       <c r="DN75" s="11" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="76" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B76" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="C76" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="D76" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="D76" s="9" t="s">
+      <c r="E76" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="E76" s="9" t="s">
+      <c r="F76" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="F76" s="9" t="s">
+      <c r="G76" s="9" t="s">
         <v>492</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>493</v>
       </c>
       <c r="H76" s="9">
         <v>0</v>
@@ -15364,10 +15352,10 @@
       <c r="DL76" s="12"/>
       <c r="DM76" s="11"/>
       <c r="DN76" s="11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
-    <row r="77" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="9" t="s">
         <v>118</v>
       </c>
@@ -15515,27 +15503,27 @@
         <v>400</v>
       </c>
     </row>
-    <row r="78" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B78" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C78" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="D78" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="D78" s="9" t="s">
+      <c r="E78" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="E78" s="9" t="s">
+      <c r="F78" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="F78" s="9" t="s">
+      <c r="G78" s="9" t="s">
         <v>499</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>500</v>
       </c>
       <c r="H78" s="9">
         <v>221</v>
@@ -15664,10 +15652,10 @@
       </c>
       <c r="DM78" s="11"/>
       <c r="DN78" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
-    <row r="79" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="9" t="s">
         <v>118</v>
       </c>
@@ -15835,7 +15823,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="80" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="9" t="s">
         <v>118</v>
       </c>
@@ -16003,27 +15991,27 @@
         <v>339</v>
       </c>
     </row>
-    <row r="81" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B81" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="D81" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="E81" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="E81" s="9" t="s">
+      <c r="F81" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="F81" s="9" t="s">
+      <c r="G81" s="9" t="s">
         <v>478</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>479</v>
       </c>
       <c r="H81" s="9">
         <v>198</v>
@@ -16156,10 +16144,10 @@
       <c r="DL81" s="12"/>
       <c r="DM81" s="11"/>
       <c r="DN81" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
-    <row r="82" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="9" t="s">
         <v>118</v>
       </c>
@@ -16327,27 +16315,27 @@
         <v>313</v>
       </c>
     </row>
-    <row r="83" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B83" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="C83" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="C83" s="9" t="s">
+      <c r="D83" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="E83" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="E83" s="9" t="s">
+      <c r="F83" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="F83" s="9" t="s">
+      <c r="G83" s="9" t="s">
         <v>449</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>450</v>
       </c>
       <c r="H83" s="9">
         <v>250</v>
@@ -16474,10 +16462,10 @@
       <c r="DL83" s="12"/>
       <c r="DM83" s="11"/>
       <c r="DN83" s="11" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
-    <row r="84" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="9" t="s">
         <v>118</v>
       </c>
@@ -16651,13 +16639,13 @@
       <c r="DK84" s="12"/>
       <c r="DL84" s="12"/>
       <c r="DM84" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="DN84" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="DN84" s="11" t="s">
-        <v>437</v>
-      </c>
     </row>
-    <row r="85" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="9" t="s">
         <v>118</v>
       </c>
@@ -16835,27 +16823,27 @@
         <v>379</v>
       </c>
     </row>
-    <row r="86" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B86" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>739</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="E86" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="F86" s="9" t="s">
         <v>741</v>
       </c>
-      <c r="E86" s="9" t="s">
+      <c r="G86" s="9" t="s">
         <v>742</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>744</v>
       </c>
       <c r="H86" s="9">
         <v>0</v>
@@ -17000,10 +16988,10 @@
       <c r="DL86" s="12"/>
       <c r="DM86" s="11"/>
       <c r="DN86" s="11" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
-    <row r="87" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="9" t="s">
         <v>118</v>
       </c>
@@ -17163,7 +17151,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="88" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="9" t="s">
         <v>118</v>
       </c>
@@ -17373,27 +17361,27 @@
         <v>270</v>
       </c>
     </row>
-    <row r="89" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B89" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="C89" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="D89" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="D89" s="9" t="s">
+      <c r="E89" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="F89" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="F89" s="9" t="s">
+      <c r="G89" s="9" t="s">
         <v>470</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>471</v>
       </c>
       <c r="H89" s="9">
         <v>50</v>
@@ -17581,13 +17569,13 @@
         <v>125</v>
       </c>
       <c r="DM89" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="DN89" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="DN89" s="11" t="s">
-        <v>473</v>
-      </c>
     </row>
-    <row r="90" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="9" t="s">
         <v>118</v>
       </c>
@@ -17791,7 +17779,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="91" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="9" t="s">
         <v>118</v>
       </c>
@@ -17953,8 +17941,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005D697BBB6C7C71438AA06DE92AE599CC" ma:contentTypeVersion="" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f36473a6175c50f896b3e1cbc3f13916">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31AAD03C-A983-4B16-863F-54F1EAB739D9" xmlns:ns3="77e41a71-2e1a-40e6-b4fe-2cfc7a738e36" xmlns:ns4="31aad03c-a983-4b16-863f-54f1eab739d9" xmlns:ns5="b1759036-c6d1-4f23-8159-9e5ddc0da7b4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f6313d8d0f967e45b58df0cfae536c6" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005D697BBB6C7C71438AA06DE92AE599CC" ma:contentTypeVersion="" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="a1eafba633277ec00883d4e10cd96e51">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31AAD03C-A983-4B16-863F-54F1EAB739D9" xmlns:ns3="77e41a71-2e1a-40e6-b4fe-2cfc7a738e36" xmlns:ns4="31aad03c-a983-4b16-863f-54f1eab739d9" xmlns:ns5="b1759036-c6d1-4f23-8159-9e5ddc0da7b4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="96273a645e27db515b242c1154665ce1" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="31AAD03C-A983-4B16-863F-54F1EAB739D9"/>
     <xsd:import namespace="77e41a71-2e1a-40e6-b4fe-2cfc7a738e36"/>
     <xsd:import namespace="31aad03c-a983-4b16-863f-54f1eab739d9"/>
@@ -18265,7 +18253,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EA674AB-B398-4A1E-8989-7222AB7F3ECF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96CF3892-8C4C-48BE-9175-E23580A94330}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -18286,7 +18274,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F6050CD-9EDE-4974-9BB2-A8A03FDD9D64}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45E6C229-B56E-41B4-A555-9A0F37FDBD3C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -18294,7 +18282,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35A85F85-E350-4528-A2D7-1C5DB622E87D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4A06469-5DF0-429E-BE57-A898F523DE61}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/data/byouin_list/org/byouin_list.xlsx
+++ b/data/byouin_list/org/byouin_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\po3filesv07\政策局データ戦略課共用\2024年度\101_データ活用推進班★\202_オープンデータ\2024\★公開中データ（HP・BODIK共通）★\29_病院一覧\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\po3filesv07\政策局データ戦略課共用\2024年度\101_データ活用推進班★\202_オープンデータ\2024\05_各課提出ファイル\R7.3\医療対策課\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{739EBA6F-79EA-42AA-9EF7-7AF298E58683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37887912-0179-4D41-A220-6B22EAD50431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="754">
   <si>
     <t>施設区分</t>
   </si>
@@ -703,7 +703,7 @@
     <t>鶴崎　成幸</t>
   </si>
   <si>
-    <t>脳神経内科 糖尿病・代謝内科</t>
+    <t>糖尿病・代謝内科</t>
   </si>
   <si>
     <t>昭和 48年07月16日</t>
@@ -991,7 +991,7 @@
     <t>木下　裕俊</t>
   </si>
   <si>
-    <t>桜十字熊本東病院</t>
+    <t>くまもと在宅支援病院</t>
   </si>
   <si>
     <t>862-0922</t>
@@ -1030,7 +1030,7 @@
     <t>防衛省</t>
   </si>
   <si>
-    <t>内藤　智子</t>
+    <t>中家　和宏</t>
   </si>
   <si>
     <t>昭和 32年08月01日</t>
@@ -1315,7 +1315,7 @@
     <t>医療法人社団　ピネル会</t>
   </si>
   <si>
-    <t>竹内　良輔</t>
+    <t>竹内　有輔</t>
   </si>
   <si>
     <t>昭和 46年11月30日</t>
@@ -1468,9 +1468,6 @@
     <t>吉田　俊彰</t>
   </si>
   <si>
-    <t>糖尿病・代謝内科</t>
-  </si>
-  <si>
     <t>昭和 26年08月01日</t>
   </si>
   <si>
@@ -1510,7 +1507,7 @@
     <t>医療法人　尚和会</t>
   </si>
   <si>
-    <t>黒木　明彦</t>
+    <t>下村　康正</t>
   </si>
   <si>
     <t>昭和 27年08月08日</t>
@@ -1849,7 +1846,7 @@
     <t>社会医療法人　寿量会</t>
   </si>
   <si>
-    <t>中島　英親</t>
+    <t>寺本　憲市郎</t>
   </si>
   <si>
     <t>小児形成外科 血管外科 脳神経内科</t>
@@ -1942,7 +1939,7 @@
     <t>昭和 60年01月31日</t>
   </si>
   <si>
-    <t>くまもと乳腺・胃腸外科病院</t>
+    <t>くまもと乳腺外科病院</t>
   </si>
   <si>
     <t xml:space="preserve">熊本市中央区南熊本4丁目3-5 </t>
@@ -1954,7 +1951,7 @@
     <t>医療法人社団　世安会</t>
   </si>
   <si>
-    <t>澤田　俊彦</t>
+    <t>村本　一浩</t>
   </si>
   <si>
     <t>乳腺内科 がん化学療法内科</t>
@@ -2044,7 +2041,7 @@
     <t>伊東歯科口腔病院</t>
   </si>
   <si>
-    <t>861-0851</t>
+    <t>860-0851</t>
   </si>
   <si>
     <t xml:space="preserve">熊本市中央区子飼本町４番１４号 </t>
@@ -2077,7 +2074,7 @@
     <t>熊本市</t>
   </si>
   <si>
-    <t>掃本　誠治</t>
+    <t>三角　郁夫</t>
   </si>
   <si>
     <t>平成 22年03月23日</t>
@@ -2161,7 +2158,7 @@
     <t>社会医療法人令和会</t>
   </si>
   <si>
-    <t>平川　敬</t>
+    <t>生田　拓也</t>
   </si>
   <si>
     <t>血管外科</t>
@@ -2260,9 +2257,6 @@
     <t>坂本　憲史</t>
   </si>
   <si>
-    <t>内視鏡内科</t>
-  </si>
-  <si>
     <t>平成 24年08月01日</t>
   </si>
   <si>
@@ -2278,7 +2272,7 @@
     <t>医療法人　堀尾会</t>
   </si>
   <si>
-    <t>平田　好文</t>
+    <t>小原　健志</t>
   </si>
   <si>
     <t>小児リハビリテーション科 脳神経内科</t>
@@ -2347,7 +2341,7 @@
     <t>社会医療法人社団高野会</t>
   </si>
   <si>
-    <t>髙野　正太</t>
+    <t>辻　順行</t>
   </si>
   <si>
     <t>肛門内科 大腸・肛門リハビリテーション科 緩和ケア内科</t>
@@ -2413,7 +2407,7 @@
     <t>医療法人社団　井上会</t>
   </si>
   <si>
-    <t>木村　竜也</t>
+    <t>井上　佳子</t>
   </si>
   <si>
     <t>昭和 56年01月01日</t>
@@ -2804,19 +2798,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:DN91"/>
-  <sheetFormatPr defaultRowHeight="24.95" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="2" customWidth="1"/>
-    <col min="8" max="12" width="4.28515625" style="2" customWidth="1"/>
-    <col min="13" max="116" width="3.7109375" style="5" customWidth="1"/>
-    <col min="117" max="118" width="18.42578125" style="4" customWidth="1"/>
-    <col min="119" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="6.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="2" customWidth="1"/>
+    <col min="8" max="12" width="4.33203125" style="2" customWidth="1"/>
+    <col min="13" max="116" width="3.6640625" style="5" customWidth="1"/>
+    <col min="117" max="118" width="18.44140625" style="4" customWidth="1"/>
+    <col min="119" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:118" s="1" customFormat="1" ht="142.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -3175,27 +3169,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:118" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:118" s="3" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>665</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>666</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>667</v>
       </c>
       <c r="H2" s="9">
         <v>0</v>
@@ -3335,33 +3329,33 @@
         <v>125</v>
       </c>
       <c r="DM2" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="DN2" s="11" t="s">
         <v>668</v>
       </c>
-      <c r="DN2" s="11" t="s">
-        <v>669</v>
-      </c>
     </row>
-    <row r="3" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>677</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>680</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>681</v>
       </c>
       <c r="H3" s="9">
         <v>0</v>
@@ -3535,33 +3529,33 @@
         <v>125</v>
       </c>
       <c r="DM3" s="11" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="DN3" s="11" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
-    <row r="4" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>520</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>521</v>
       </c>
       <c r="H4" s="9">
         <v>0</v>
@@ -3699,33 +3693,33 @@
       <c r="DK4" s="12"/>
       <c r="DL4" s="12"/>
       <c r="DM4" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="DN4" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="DN4" s="11" t="s">
-        <v>523</v>
-      </c>
     </row>
-    <row r="5" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>727</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>729</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -3865,33 +3859,33 @@
         <v>125</v>
       </c>
       <c r="DM5" s="11" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="DN5" s="11" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
-    <row r="6" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>199</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>734</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>736</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -4051,33 +4045,33 @@
         <v>125</v>
       </c>
       <c r="DM6" s="11" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="DN6" s="11" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="7" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>711</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>712</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>714</v>
       </c>
       <c r="H7" s="9">
         <v>193</v>
@@ -4202,30 +4196,30 @@
       <c r="DL7" s="12"/>
       <c r="DM7" s="11"/>
       <c r="DN7" s="11" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
-    <row r="8" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>716</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>719</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>721</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -4323,7 +4317,9 @@
       <c r="BY8" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="BZ8" s="12"/>
+      <c r="BZ8" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="CA8" s="12"/>
       <c r="CB8" s="12"/>
       <c r="CC8" s="12"/>
@@ -4367,33 +4363,33 @@
         <v>125</v>
       </c>
       <c r="DM8" s="11" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="DN8" s="11" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
-    <row r="9" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>207</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>704</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>706</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -4529,33 +4525,33 @@
       <c r="DK9" s="12"/>
       <c r="DL9" s="12"/>
       <c r="DM9" s="11" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="DN9" s="11" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
-    <row r="10" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>696</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>698</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>699</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -4577,9 +4573,7 @@
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
-      <c r="P10" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
@@ -4608,9 +4602,7 @@
       <c r="AP10" s="12"/>
       <c r="AQ10" s="12"/>
       <c r="AR10" s="12"/>
-      <c r="AS10" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="AS10" s="12"/>
       <c r="AT10" s="12"/>
       <c r="AU10" s="12"/>
       <c r="AV10" s="12"/>
@@ -4619,7 +4611,9 @@
       <c r="AY10" s="12"/>
       <c r="AZ10" s="12"/>
       <c r="BA10" s="12"/>
-      <c r="BB10" s="12"/>
+      <c r="BB10" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="BC10" s="12"/>
       <c r="BD10" s="12"/>
       <c r="BE10" s="12"/>
@@ -4640,7 +4634,9 @@
       <c r="BT10" s="12"/>
       <c r="BU10" s="12"/>
       <c r="BV10" s="12"/>
-      <c r="BW10" s="12"/>
+      <c r="BW10" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="BX10" s="12"/>
       <c r="BY10" s="12"/>
       <c r="BZ10" s="12"/>
@@ -4683,35 +4679,35 @@
       <c r="DI10" s="12"/>
       <c r="DJ10" s="12"/>
       <c r="DK10" s="12"/>
-      <c r="DL10" s="12"/>
-      <c r="DM10" s="11" t="s">
-        <v>700</v>
-      </c>
+      <c r="DL10" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="DM10" s="11"/>
       <c r="DN10" s="11" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
-    <row r="11" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>319</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>690</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>691</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>370</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -4846,30 +4842,30 @@
         <v>196</v>
       </c>
       <c r="DN11" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
-    <row r="12" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>144</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>595</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>597</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>598</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -4942,17 +4938,11 @@
       <c r="BJ12" s="12"/>
       <c r="BK12" s="12"/>
       <c r="BL12" s="12"/>
-      <c r="BM12" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BM12" s="12"/>
       <c r="BN12" s="12"/>
-      <c r="BO12" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BO12" s="12"/>
       <c r="BP12" s="12"/>
-      <c r="BQ12" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BQ12" s="12"/>
       <c r="BR12" s="12"/>
       <c r="BS12" s="12"/>
       <c r="BT12" s="12"/>
@@ -5005,33 +4995,33 @@
         <v>125</v>
       </c>
       <c r="DM12" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="DN12" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="DN12" s="11" t="s">
-        <v>600</v>
-      </c>
     </row>
-    <row r="13" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>265</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>686</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>687</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -5160,30 +5150,30 @@
       <c r="DL13" s="12"/>
       <c r="DM13" s="11"/>
       <c r="DN13" s="11" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
-    <row r="14" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>634</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>637</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>638</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>639</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -5320,30 +5310,30 @@
       <c r="DL14" s="12"/>
       <c r="DM14" s="11"/>
       <c r="DN14" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
-    <row r="15" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>630</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>631</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>632</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -5476,30 +5466,30 @@
       </c>
       <c r="DM15" s="11"/>
       <c r="DN15" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
-    <row r="16" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>144</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>622</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="F16" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>623</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>624</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -5540,9 +5530,7 @@
       <c r="X16" s="12"/>
       <c r="Y16" s="12"/>
       <c r="Z16" s="12"/>
-      <c r="AA16" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="AA16" s="12"/>
       <c r="AB16" s="12"/>
       <c r="AC16" s="12"/>
       <c r="AD16" s="12"/>
@@ -5645,33 +5633,33 @@
       <c r="DK16" s="12"/>
       <c r="DL16" s="12"/>
       <c r="DM16" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="DN16" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="DN16" s="11" t="s">
-        <v>626</v>
-      </c>
     </row>
-    <row r="17" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>609</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>610</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>611</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>612</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -5808,10 +5796,10 @@
       </c>
       <c r="DM17" s="11"/>
       <c r="DN17" s="11" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
-    <row r="18" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9" t="s">
         <v>118</v>
       </c>
@@ -5963,7 +5951,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="19" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="9" t="s">
         <v>118</v>
       </c>
@@ -6121,27 +6109,27 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>251</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="F20" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>604</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>605</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -6280,30 +6268,30 @@
       </c>
       <c r="DM20" s="11"/>
       <c r="DN20" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
-    <row r="21" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>505</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>506</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -6433,13 +6421,13 @@
       <c r="DK21" s="12"/>
       <c r="DL21" s="12"/>
       <c r="DM21" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="DN21" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="DN21" s="11" t="s">
-        <v>508</v>
-      </c>
     </row>
-    <row r="22" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="9" t="s">
         <v>118</v>
       </c>
@@ -6595,7 +6583,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="23" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="9" t="s">
         <v>118</v>
       </c>
@@ -6755,7 +6743,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="24" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="9" t="s">
         <v>118</v>
       </c>
@@ -6925,7 +6913,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="25" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="9" t="s">
         <v>118</v>
       </c>
@@ -7097,7 +7085,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="26" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="9" t="s">
         <v>118</v>
       </c>
@@ -7245,7 +7233,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="27" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="9" t="s">
         <v>118</v>
       </c>
@@ -7403,7 +7391,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>118</v>
       </c>
@@ -7591,7 +7579,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="9" t="s">
         <v>118</v>
       </c>
@@ -7749,7 +7737,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="30" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="9" t="s">
         <v>118</v>
       </c>
@@ -7913,7 +7901,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="31" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="9" t="s">
         <v>118</v>
       </c>
@@ -8103,7 +8091,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="32" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="9" t="s">
         <v>118</v>
       </c>
@@ -8261,7 +8249,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="9" t="s">
         <v>118</v>
       </c>
@@ -8411,7 +8399,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="9" t="s">
         <v>118</v>
       </c>
@@ -8559,27 +8547,27 @@
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B35" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="D35" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="E35" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="F35" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="G35" s="9" t="s">
         <v>513</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>514</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -8723,13 +8711,13 @@
         <v>125</v>
       </c>
       <c r="DM35" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="DN35" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="DN35" s="11" t="s">
-        <v>516</v>
-      </c>
     </row>
-    <row r="36" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="9" t="s">
         <v>118</v>
       </c>
@@ -8907,27 +8895,27 @@
         <v>422</v>
       </c>
     </row>
-    <row r="37" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B37" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="D37" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="E37" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="F37" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="G37" s="9" t="s">
         <v>549</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>550</v>
       </c>
       <c r="H37" s="9">
         <v>135</v>
@@ -9054,10 +9042,10 @@
       <c r="DL37" s="12"/>
       <c r="DM37" s="11"/>
       <c r="DN37" s="11" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="9" t="s">
         <v>118</v>
       </c>
@@ -9167,7 +9155,9 @@
       <c r="CC38" s="12"/>
       <c r="CD38" s="12"/>
       <c r="CE38" s="12"/>
-      <c r="CF38" s="12"/>
+      <c r="CF38" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="CG38" s="12"/>
       <c r="CH38" s="12"/>
       <c r="CI38" s="12"/>
@@ -9207,27 +9197,27 @@
         <v>205</v>
       </c>
     </row>
-    <row r="39" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B39" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="D39" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="E39" s="9" t="s">
         <v>643</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="F39" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="G39" s="9" t="s">
         <v>645</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>646</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -9366,10 +9356,10 @@
       </c>
       <c r="DM39" s="11"/>
       <c r="DN39" s="11" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
-    <row r="40" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="9" t="s">
         <v>118</v>
       </c>
@@ -9526,10 +9516,10 @@
       <c r="DL40" s="12"/>
       <c r="DM40" s="11"/>
       <c r="DN40" s="11" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
-    <row r="41" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="9" t="s">
         <v>118</v>
       </c>
@@ -9708,10 +9698,10 @@
       </c>
       <c r="DM41" s="11"/>
       <c r="DN41" s="11" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
-    <row r="42" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="9" t="s">
         <v>118</v>
       </c>
@@ -9877,7 +9867,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="43" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="9" t="s">
         <v>118</v>
       </c>
@@ -10027,7 +10017,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="44" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="9" t="s">
         <v>118</v>
       </c>
@@ -10181,27 +10171,27 @@
         <v>168</v>
       </c>
     </row>
-    <row r="45" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>251</v>
       </c>
       <c r="D45" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="F45" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="G45" s="9" t="s">
         <v>591</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>592</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -10340,30 +10330,30 @@
       </c>
       <c r="DM45" s="11"/>
       <c r="DN45" s="11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
-    <row r="46" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B46" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="D46" s="9" t="s">
+      <c r="E46" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="F46" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="G46" s="9" t="s">
         <v>541</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>542</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -10478,7 +10468,9 @@
       <c r="BR46" s="12"/>
       <c r="BS46" s="12"/>
       <c r="BT46" s="12"/>
-      <c r="BU46" s="12"/>
+      <c r="BU46" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="BV46" s="12"/>
       <c r="BW46" s="12" t="s">
         <v>125</v>
@@ -10549,13 +10541,13 @@
         <v>125</v>
       </c>
       <c r="DM46" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="DN46" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="DN46" s="11" t="s">
-        <v>544</v>
-      </c>
     </row>
-    <row r="47" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="9" t="s">
         <v>118</v>
       </c>
@@ -10717,27 +10709,27 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B48" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="D48" s="9" t="s">
+      <c r="E48" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="F48" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="G48" s="9" t="s">
         <v>555</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>556</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -10866,30 +10858,30 @@
       <c r="DL48" s="12"/>
       <c r="DM48" s="11"/>
       <c r="DN48" s="11" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
-    <row r="49" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B49" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="D49" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="E49" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="F49" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="G49" s="9" t="s">
         <v>562</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>563</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -10985,9 +10977,7 @@
       <c r="BW49" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="BX49" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BX49" s="12"/>
       <c r="BY49" s="12" t="s">
         <v>125</v>
       </c>
@@ -11041,13 +11031,13 @@
         <v>125</v>
       </c>
       <c r="DM49" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="DN49" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="DN49" s="11" t="s">
-        <v>565</v>
-      </c>
     </row>
-    <row r="50" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="9" t="s">
         <v>118</v>
       </c>
@@ -11223,27 +11213,27 @@
         <v>352</v>
       </c>
     </row>
-    <row r="51" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B51" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="E51" s="9" t="s">
         <v>747</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="F51" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="G51" s="9" t="s">
         <v>749</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>751</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -11370,10 +11360,10 @@
       <c r="DL51" s="12"/>
       <c r="DM51" s="11"/>
       <c r="DN51" s="11" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
-    <row r="52" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="9" t="s">
         <v>118</v>
       </c>
@@ -11429,9 +11419,7 @@
       <c r="AA52" s="12"/>
       <c r="AB52" s="12"/>
       <c r="AC52" s="12"/>
-      <c r="AD52" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="AD52" s="12"/>
       <c r="AE52" s="12"/>
       <c r="AF52" s="12"/>
       <c r="AG52" s="12"/>
@@ -11446,7 +11434,9 @@
       <c r="AP52" s="12"/>
       <c r="AQ52" s="12"/>
       <c r="AR52" s="12"/>
-      <c r="AS52" s="12"/>
+      <c r="AS52" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="AT52" s="12"/>
       <c r="AU52" s="12"/>
       <c r="AV52" s="12"/>
@@ -11531,27 +11521,27 @@
         <v>414</v>
       </c>
     </row>
-    <row r="53" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B53" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="C53" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="D53" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="E53" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="F53" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="G53" s="9" t="s">
         <v>570</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>571</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
@@ -11678,10 +11668,10 @@
       </c>
       <c r="DM53" s="11"/>
       <c r="DN53" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
-    <row r="54" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="9" t="s">
         <v>118</v>
       </c>
@@ -11833,27 +11823,27 @@
         <v>365</v>
       </c>
     </row>
-    <row r="55" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B55" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="C55" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="D55" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="E55" s="9" t="s">
         <v>532</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="F55" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="G55" s="9" t="s">
         <v>534</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>535</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
@@ -11981,33 +11971,33 @@
         <v>125</v>
       </c>
       <c r="DM55" s="11" t="s">
+        <v>535</v>
+      </c>
+      <c r="DN55" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="DN55" s="11" t="s">
-        <v>537</v>
-      </c>
     </row>
-    <row r="56" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B56" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="C56" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="D56" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="E56" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="F56" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="G56" s="9" t="s">
         <v>527</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>528</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -12148,30 +12138,30 @@
       <c r="DL56" s="12"/>
       <c r="DM56" s="11"/>
       <c r="DN56" s="11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
-    <row r="57" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B57" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C57" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="D57" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="E57" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="F57" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="G57" s="9" t="s">
         <v>442</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>443</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -12318,10 +12308,10 @@
       <c r="DL57" s="12"/>
       <c r="DM57" s="11"/>
       <c r="DN57" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="58" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="9" t="s">
         <v>118</v>
       </c>
@@ -12475,7 +12465,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="59" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="9" t="s">
         <v>118</v>
       </c>
@@ -12633,27 +12623,27 @@
         <v>372</v>
       </c>
     </row>
-    <row r="60" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B60" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="C60" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="D60" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="E60" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="F60" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="G60" s="9" t="s">
         <v>618</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>619</v>
       </c>
       <c r="H60" s="9">
         <v>190</v>
@@ -12784,10 +12774,10 @@
       <c r="DL60" s="12"/>
       <c r="DM60" s="11"/>
       <c r="DN60" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
-    <row r="61" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="9" t="s">
         <v>118</v>
       </c>
@@ -12878,9 +12868,7 @@
       <c r="BB61" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="BC61" s="12" t="s">
-        <v>125</v>
-      </c>
+      <c r="BC61" s="12"/>
       <c r="BD61" s="12"/>
       <c r="BE61" s="12"/>
       <c r="BF61" s="12"/>
@@ -12955,7 +12943,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="9" t="s">
         <v>118</v>
       </c>
@@ -13125,27 +13113,27 @@
         <v>325</v>
       </c>
     </row>
-    <row r="63" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B63" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="C63" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="D63" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="E63" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="F63" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="F63" s="9" t="s">
+      <c r="G63" s="9" t="s">
         <v>584</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>585</v>
       </c>
       <c r="H63" s="9">
         <v>0</v>
@@ -13236,7 +13224,9 @@
       <c r="BT63" s="12"/>
       <c r="BU63" s="12"/>
       <c r="BV63" s="12"/>
-      <c r="BW63" s="12"/>
+      <c r="BW63" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="BX63" s="12"/>
       <c r="BY63" s="12"/>
       <c r="BZ63" s="12"/>
@@ -13283,13 +13273,13 @@
       <c r="DK63" s="12"/>
       <c r="DL63" s="12"/>
       <c r="DM63" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="DN63" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="DN63" s="11" t="s">
-        <v>587</v>
-      </c>
     </row>
-    <row r="64" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="9" t="s">
         <v>118</v>
       </c>
@@ -13473,7 +13463,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="65" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="9" t="s">
         <v>118</v>
       </c>
@@ -13623,27 +13613,27 @@
         <v>386</v>
       </c>
     </row>
-    <row r="66" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B66" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="D66" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="E66" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="E66" s="9" t="s">
+      <c r="F66" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="G66" s="9" t="s">
         <v>485</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>486</v>
       </c>
       <c r="H66" s="9">
         <v>234</v>
@@ -13770,30 +13760,30 @@
       <c r="DL66" s="12"/>
       <c r="DM66" s="11"/>
       <c r="DN66" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
-    <row r="67" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B67" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="C67" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="D67" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="E67" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="F67" s="9" t="s">
         <v>673</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="G67" s="9" t="s">
         <v>674</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>675</v>
       </c>
       <c r="H67" s="9">
         <v>78</v>
@@ -13944,10 +13934,10 @@
         <v>196</v>
       </c>
       <c r="DN67" s="11" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
-    <row r="68" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="9" t="s">
         <v>118</v>
       </c>
@@ -14103,27 +14093,27 @@
         <v>345</v>
       </c>
     </row>
-    <row r="69" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B69" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="C69" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="D69" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="D69" s="9" t="s">
+      <c r="E69" s="9" t="s">
         <v>657</v>
       </c>
-      <c r="E69" s="9" t="s">
+      <c r="F69" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="F69" s="9" t="s">
+      <c r="G69" s="9" t="s">
         <v>659</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>660</v>
       </c>
       <c r="H69" s="9">
         <v>0</v>
@@ -14258,30 +14248,30 @@
       <c r="DL69" s="12"/>
       <c r="DM69" s="11"/>
       <c r="DN69" s="11" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
-    <row r="70" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B70" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="C70" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="D70" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="D70" s="9" t="s">
+      <c r="E70" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="E70" s="9" t="s">
+      <c r="F70" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="F70" s="9" t="s">
+      <c r="G70" s="9" t="s">
         <v>577</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>578</v>
       </c>
       <c r="H70" s="9">
         <v>0</v>
@@ -14426,30 +14416,30 @@
       <c r="DL70" s="12"/>
       <c r="DM70" s="11"/>
       <c r="DN70" s="11" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
-    <row r="71" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B71" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="C71" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="D71" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="E71" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="E71" s="9" t="s">
+      <c r="F71" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="G71" s="9" t="s">
         <v>456</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>457</v>
       </c>
       <c r="H71" s="9">
         <v>160</v>
@@ -14574,30 +14564,30 @@
       <c r="DL71" s="12"/>
       <c r="DM71" s="11"/>
       <c r="DN71" s="11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
-    <row r="72" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B72" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="C72" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="D72" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="D72" s="9" t="s">
+      <c r="E72" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="E72" s="9" t="s">
+      <c r="F72" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="G72" s="9" t="s">
         <v>652</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>653</v>
       </c>
       <c r="H72" s="9">
         <v>198</v>
@@ -14726,10 +14716,10 @@
       <c r="DL72" s="12"/>
       <c r="DM72" s="11"/>
       <c r="DN72" s="11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
-    <row r="73" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="9" t="s">
         <v>118</v>
       </c>
@@ -14877,7 +14867,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="74" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="9" t="s">
         <v>118</v>
       </c>
@@ -15053,27 +15043,27 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B75" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C75" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="D75" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="D75" s="9" t="s">
+      <c r="E75" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="E75" s="9" t="s">
+      <c r="F75" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="F75" s="9" t="s">
+      <c r="G75" s="9" t="s">
         <v>463</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>464</v>
       </c>
       <c r="H75" s="9">
         <v>199</v>
@@ -15200,30 +15190,30 @@
       <c r="DL75" s="12"/>
       <c r="DM75" s="11"/>
       <c r="DN75" s="11" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="76" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B76" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="C76" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="D76" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="D76" s="9" t="s">
+      <c r="E76" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="E76" s="9" t="s">
+      <c r="F76" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="F76" s="9" t="s">
+      <c r="G76" s="9" t="s">
         <v>492</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>493</v>
       </c>
       <c r="H76" s="9">
         <v>0</v>
@@ -15364,10 +15354,10 @@
       <c r="DL76" s="12"/>
       <c r="DM76" s="11"/>
       <c r="DN76" s="11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
-    <row r="77" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="9" t="s">
         <v>118</v>
       </c>
@@ -15515,27 +15505,27 @@
         <v>400</v>
       </c>
     </row>
-    <row r="78" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B78" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C78" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="D78" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="D78" s="9" t="s">
+      <c r="E78" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="E78" s="9" t="s">
+      <c r="F78" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="F78" s="9" t="s">
+      <c r="G78" s="9" t="s">
         <v>499</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>500</v>
       </c>
       <c r="H78" s="9">
         <v>221</v>
@@ -15664,10 +15654,10 @@
       </c>
       <c r="DM78" s="11"/>
       <c r="DN78" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
-    <row r="79" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="9" t="s">
         <v>118</v>
       </c>
@@ -15835,7 +15825,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="80" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="9" t="s">
         <v>118</v>
       </c>
@@ -16003,27 +15993,27 @@
         <v>339</v>
       </c>
     </row>
-    <row r="81" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B81" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="D81" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="E81" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="E81" s="9" t="s">
+      <c r="F81" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="F81" s="9" t="s">
+      <c r="G81" s="9" t="s">
         <v>478</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>479</v>
       </c>
       <c r="H81" s="9">
         <v>198</v>
@@ -16156,10 +16146,10 @@
       <c r="DL81" s="12"/>
       <c r="DM81" s="11"/>
       <c r="DN81" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
-    <row r="82" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="9" t="s">
         <v>118</v>
       </c>
@@ -16327,27 +16317,27 @@
         <v>313</v>
       </c>
     </row>
-    <row r="83" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B83" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="C83" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="C83" s="9" t="s">
+      <c r="D83" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="E83" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="E83" s="9" t="s">
+      <c r="F83" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="F83" s="9" t="s">
+      <c r="G83" s="9" t="s">
         <v>449</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>450</v>
       </c>
       <c r="H83" s="9">
         <v>250</v>
@@ -16474,10 +16464,10 @@
       <c r="DL83" s="12"/>
       <c r="DM83" s="11"/>
       <c r="DN83" s="11" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
-    <row r="84" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="9" t="s">
         <v>118</v>
       </c>
@@ -16651,13 +16641,13 @@
       <c r="DK84" s="12"/>
       <c r="DL84" s="12"/>
       <c r="DM84" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="DN84" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="DN84" s="11" t="s">
-        <v>437</v>
-      </c>
     </row>
-    <row r="85" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="9" t="s">
         <v>118</v>
       </c>
@@ -16835,27 +16825,27 @@
         <v>379</v>
       </c>
     </row>
-    <row r="86" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B86" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>739</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="E86" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="F86" s="9" t="s">
         <v>741</v>
       </c>
-      <c r="E86" s="9" t="s">
+      <c r="G86" s="9" t="s">
         <v>742</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>744</v>
       </c>
       <c r="H86" s="9">
         <v>0</v>
@@ -17000,10 +16990,10 @@
       <c r="DL86" s="12"/>
       <c r="DM86" s="11"/>
       <c r="DN86" s="11" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
-    <row r="87" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="9" t="s">
         <v>118</v>
       </c>
@@ -17163,7 +17153,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="88" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="9" t="s">
         <v>118</v>
       </c>
@@ -17373,27 +17363,27 @@
         <v>270</v>
       </c>
     </row>
-    <row r="89" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B89" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="C89" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="D89" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="D89" s="9" t="s">
+      <c r="E89" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="F89" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="F89" s="9" t="s">
+      <c r="G89" s="9" t="s">
         <v>470</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>471</v>
       </c>
       <c r="H89" s="9">
         <v>50</v>
@@ -17581,13 +17571,13 @@
         <v>125</v>
       </c>
       <c r="DM89" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="DN89" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="DN89" s="11" t="s">
-        <v>473</v>
-      </c>
     </row>
-    <row r="90" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="9" t="s">
         <v>118</v>
       </c>
@@ -17791,7 +17781,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="91" spans="1:118" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:118" ht="25.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="9" t="s">
         <v>118</v>
       </c>
@@ -17953,8 +17943,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005D697BBB6C7C71438AA06DE92AE599CC" ma:contentTypeVersion="" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f36473a6175c50f896b3e1cbc3f13916">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31AAD03C-A983-4B16-863F-54F1EAB739D9" xmlns:ns3="77e41a71-2e1a-40e6-b4fe-2cfc7a738e36" xmlns:ns4="31aad03c-a983-4b16-863f-54f1eab739d9" xmlns:ns5="b1759036-c6d1-4f23-8159-9e5ddc0da7b4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f6313d8d0f967e45b58df0cfae536c6" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005D697BBB6C7C71438AA06DE92AE599CC" ma:contentTypeVersion="" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="216f331b4d3aa8008f35022f7d74240d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31AAD03C-A983-4B16-863F-54F1EAB739D9" xmlns:ns3="77e41a71-2e1a-40e6-b4fe-2cfc7a738e36" xmlns:ns4="31aad03c-a983-4b16-863f-54f1eab739d9" xmlns:ns5="b1759036-c6d1-4f23-8159-9e5ddc0da7b4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a41bd4b8d4f39fe761a1445c1a60a7ab" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="31AAD03C-A983-4B16-863F-54F1EAB739D9"/>
     <xsd:import namespace="77e41a71-2e1a-40e6-b4fe-2cfc7a738e36"/>
     <xsd:import namespace="31aad03c-a983-4b16-863f-54f1eab739d9"/>
@@ -17985,6 +17975,7 @@
                 <xsd:element ref="ns5:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns4:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns4:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -18122,6 +18113,11 @@
       </xsd:simpleType>
     </xsd:element>
     <xsd:element name="MediaServiceSearchProperties" ma:index="28" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="29" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
@@ -18265,7 +18261,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EA674AB-B398-4A1E-8989-7222AB7F3ECF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A1B613D-CA1F-4063-8F9B-35FA94698213}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -18286,7 +18282,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F6050CD-9EDE-4974-9BB2-A8A03FDD9D64}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{385E7C06-B979-49FF-B1F6-653E142727BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -18294,7 +18290,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35A85F85-E350-4528-A2D7-1C5DB622E87D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4116600A-F37F-4BD0-9B44-2096484D64E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
